--- a/Caracterizacion_Haces/data/z6mm-852.xlsx
+++ b/Caracterizacion_Haces/data/z6mm-852.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="150">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,331 +128,352 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-709,0</t>
-  </si>
-  <si>
-    <t>101,2</t>
-  </si>
-  <si>
-    <t>127,3</t>
-  </si>
-  <si>
-    <t>131,9</t>
-  </si>
-  <si>
-    <t>95,11</t>
-  </si>
-  <si>
-    <t>89,28</t>
-  </si>
-  <si>
-    <t>110,1</t>
+    <t>774,4</t>
+  </si>
+  <si>
+    <t>103,4</t>
+  </si>
+  <si>
+    <t>122,4</t>
+  </si>
+  <si>
+    <t>130,9</t>
+  </si>
+  <si>
+    <t>92,35</t>
+  </si>
+  <si>
+    <t>87,51</t>
+  </si>
+  <si>
+    <t>102,1</t>
   </si>
   <si>
     <t>0,2</t>
   </si>
   <si>
-    <t>-707,9</t>
+    <t>773,6</t>
+  </si>
+  <si>
+    <t>103,9</t>
+  </si>
+  <si>
+    <t>122,5</t>
+  </si>
+  <si>
+    <t>131,4</t>
+  </si>
+  <si>
+    <t>92,36</t>
+  </si>
+  <si>
+    <t>88,07</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>776,5</t>
+  </si>
+  <si>
+    <t>105,3</t>
+  </si>
+  <si>
+    <t>123,1</t>
+  </si>
+  <si>
+    <t>132,6</t>
+  </si>
+  <si>
+    <t>93,05</t>
+  </si>
+  <si>
+    <t>87,75</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>774,7</t>
+  </si>
+  <si>
+    <t>103,7</t>
+  </si>
+  <si>
+    <t>123,3</t>
+  </si>
+  <si>
+    <t>132,1</t>
+  </si>
+  <si>
+    <t>92,16</t>
+  </si>
+  <si>
+    <t>88,47</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>773,9</t>
+  </si>
+  <si>
+    <t>103,3</t>
+  </si>
+  <si>
+    <t>123,2</t>
+  </si>
+  <si>
+    <t>131,8</t>
+  </si>
+  <si>
+    <t>92,10</t>
+  </si>
+  <si>
+    <t>88,50</t>
+  </si>
+  <si>
+    <t>102,3</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>122,7</t>
+  </si>
+  <si>
+    <t>131,3</t>
+  </si>
+  <si>
+    <t>92,33</t>
+  </si>
+  <si>
+    <t>88,15</t>
+  </si>
+  <si>
+    <t>102,2</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>774,9</t>
+  </si>
+  <si>
+    <t>131,1</t>
+  </si>
+  <si>
+    <t>92,13</t>
+  </si>
+  <si>
+    <t>88,28</t>
   </si>
   <si>
     <t>102,4</t>
   </si>
   <si>
-    <t>128,0</t>
-  </si>
-  <si>
-    <t>133,3</t>
-  </si>
-  <si>
-    <t>95,46</t>
-  </si>
-  <si>
-    <t>89,71</t>
-  </si>
-  <si>
-    <t>110,3</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>-708,7</t>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>122,3</t>
+  </si>
+  <si>
+    <t>131,0</t>
+  </si>
+  <si>
+    <t>92,69</t>
+  </si>
+  <si>
+    <t>88,14</t>
+  </si>
+  <si>
+    <t>102,0</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>774,1</t>
+  </si>
+  <si>
+    <t>103,1</t>
+  </si>
+  <si>
+    <t>130,8</t>
+  </si>
+  <si>
+    <t>88,63</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>104,6</t>
+  </si>
+  <si>
+    <t>122,0</t>
+  </si>
+  <si>
+    <t>87,86</t>
+  </si>
+  <si>
+    <t>101,7</t>
+  </si>
+  <si>
+    <t>2,0</t>
   </si>
   <si>
     <t>102,9</t>
   </si>
   <si>
-    <t>127,6</t>
-  </si>
-  <si>
-    <t>132,9</t>
-  </si>
-  <si>
-    <t>95,98</t>
-  </si>
-  <si>
-    <t>89,37</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>-708,2</t>
-  </si>
-  <si>
-    <t>126,9</t>
+    <t>123,0</t>
+  </si>
+  <si>
+    <t>131,5</t>
+  </si>
+  <si>
+    <t>91,92</t>
+  </si>
+  <si>
+    <t>88,62</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>775,2</t>
+  </si>
+  <si>
+    <t>104,0</t>
+  </si>
+  <si>
+    <t>122,2</t>
+  </si>
+  <si>
+    <t>131,2</t>
+  </si>
+  <si>
+    <t>92,45</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>104,1</t>
+  </si>
+  <si>
+    <t>123,5</t>
   </si>
   <si>
     <t>132,4</t>
   </si>
   <si>
-    <t>95,74</t>
-  </si>
-  <si>
-    <t>90,09</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>-707,4</t>
+    <t>92,46</t>
+  </si>
+  <si>
+    <t>88,37</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>122,1</t>
+  </si>
+  <si>
+    <t>92,61</t>
+  </si>
+  <si>
+    <t>88,39</t>
+  </si>
+  <si>
+    <t>102,5</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>772,5</t>
+  </si>
+  <si>
+    <t>121,9</t>
+  </si>
+  <si>
+    <t>129,6</t>
+  </si>
+  <si>
+    <t>92,29</t>
+  </si>
+  <si>
+    <t>88,56</t>
   </si>
   <si>
     <t>101,8</t>
   </si>
   <si>
-    <t>127,7</t>
-  </si>
-  <si>
-    <t>132,5</t>
-  </si>
-  <si>
-    <t>95,42</t>
-  </si>
-  <si>
-    <t>89,85</t>
-  </si>
-  <si>
-    <t>110,4</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>-708,4</t>
-  </si>
-  <si>
-    <t>101,7</t>
-  </si>
-  <si>
-    <t>128,4</t>
-  </si>
-  <si>
-    <t>133,2</t>
-  </si>
-  <si>
-    <t>95,27</t>
-  </si>
-  <si>
-    <t>89,46</t>
-  </si>
-  <si>
-    <t>109,9</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>102,6</t>
-  </si>
-  <si>
-    <t>127,8</t>
-  </si>
-  <si>
-    <t>95,53</t>
-  </si>
-  <si>
-    <t>89,29</t>
-  </si>
-  <si>
-    <t>110,5</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>-709,5</t>
-  </si>
-  <si>
-    <t>102,5</t>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>102,7</t>
+  </si>
+  <si>
+    <t>122,6</t>
+  </si>
+  <si>
+    <t>130,7</t>
+  </si>
+  <si>
+    <t>92,24</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>92,34</t>
+  </si>
+  <si>
+    <t>88,30</t>
+  </si>
+  <si>
+    <t>3,4</t>
   </si>
   <si>
     <t>132,2</t>
   </si>
   <si>
-    <t>96,08</t>
-  </si>
-  <si>
-    <t>89,91</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>128,1</t>
-  </si>
-  <si>
-    <t>95,92</t>
-  </si>
-  <si>
-    <t>89,34</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>102,2</t>
-  </si>
-  <si>
-    <t>95,36</t>
-  </si>
-  <si>
-    <t>89,33</t>
-  </si>
-  <si>
-    <t>110,2</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>-709,2</t>
+    <t>91,86</t>
+  </si>
+  <si>
+    <t>88,45</t>
   </si>
   <si>
     <t>101,9</t>
   </si>
   <si>
-    <t>95,55</t>
-  </si>
-  <si>
-    <t>89,53</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>102,7</t>
-  </si>
-  <si>
-    <t>127,4</t>
-  </si>
-  <si>
-    <t>132,6</t>
-  </si>
-  <si>
-    <t>95,91</t>
-  </si>
-  <si>
-    <t>89,11</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>102,3</t>
-  </si>
-  <si>
-    <t>95,59</t>
-  </si>
-  <si>
-    <t>89,52</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>103,0</t>
-  </si>
-  <si>
-    <t>96,11</t>
-  </si>
-  <si>
-    <t>89,90</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>127,2</t>
-  </si>
-  <si>
-    <t>132,3</t>
-  </si>
-  <si>
-    <t>95,79</t>
-  </si>
-  <si>
-    <t>89,84</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>95,68</t>
-  </si>
-  <si>
-    <t>89,74</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>102,8</t>
-  </si>
-  <si>
-    <t>127,1</t>
-  </si>
-  <si>
-    <t>89,64</t>
-  </si>
-  <si>
-    <t>3,4</t>
-  </si>
-  <si>
-    <t>126,5</t>
-  </si>
-  <si>
-    <t>131,4</t>
-  </si>
-  <si>
-    <t>96,39</t>
-  </si>
-  <si>
-    <t>89,98</t>
-  </si>
-  <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>96,06</t>
-  </si>
-  <si>
-    <t>89,47</t>
+    <t>103,5</t>
+  </si>
+  <si>
+    <t>123,4</t>
+  </si>
+  <si>
+    <t>92,22</t>
+  </si>
+  <si>
+    <t>87,94</t>
   </si>
   <si>
     <t>3,8</t>
   </si>
   <si>
-    <t>103,2</t>
-  </si>
-  <si>
-    <t>132,8</t>
-  </si>
-  <si>
-    <t>96,21</t>
-  </si>
-  <si>
-    <t>89,30</t>
+    <t>130,4</t>
+  </si>
+  <si>
+    <t>91,82</t>
+  </si>
+  <si>
+    <t>88,16</t>
   </si>
 </sst>
 </file>
@@ -793,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -801,7 +822,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59357638888888886</v>
+        <v>0.76953703703703702</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -942,7 +963,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2754</v>
+        <v>1060</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -971,7 +992,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2753</v>
+        <v>1058</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -989,50 +1010,50 @@
         <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25">
+        <v>1062</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="C25">
-        <v>2755</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>54</v>
       </c>
-      <c r="H25" t="s">
-        <v>55</v>
-      </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" t="s">
         <v>56</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26">
+        <v>1058</v>
+      </c>
+      <c r="D26" t="s">
         <v>57</v>
-      </c>
-      <c r="C26">
-        <v>2758</v>
-      </c>
-      <c r="D26" t="s">
-        <v>51</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -1047,7 +1068,7 @@
         <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1058,7 +1079,7 @@
         <v>63</v>
       </c>
       <c r="C27">
-        <v>2757</v>
+        <v>1058</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
@@ -1084,164 +1105,164 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>1060</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
         <v>71</v>
       </c>
-      <c r="C28">
-        <v>2757</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>72</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>73</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>74</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>75</v>
-      </c>
-      <c r="H28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I28" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29">
+        <v>1060</v>
+      </c>
+      <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
         <v>78</v>
       </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29">
-        <v>2755</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="G29" t="s">
         <v>79</v>
       </c>
-      <c r="E29" t="s">
+      <c r="H29" t="s">
         <v>80</v>
       </c>
-      <c r="F29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>81</v>
-      </c>
-      <c r="H29" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30">
+        <v>1062</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" t="s">
         <v>84</v>
       </c>
-      <c r="B30" t="s">
+      <c r="G30" t="s">
         <v>85</v>
       </c>
-      <c r="C30">
-        <v>2754</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="H30" t="s">
         <v>86</v>
       </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="I30" t="s">
         <v>87</v>
-      </c>
-      <c r="G30" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31">
+        <v>1058</v>
+      </c>
+      <c r="D31" t="s">
         <v>90</v>
       </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31">
-        <v>2756</v>
-      </c>
-      <c r="D31" t="s">
-        <v>79</v>
-      </c>
       <c r="E31" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" t="s">
         <v>91</v>
       </c>
-      <c r="F31" t="s">
-        <v>74</v>
-      </c>
       <c r="G31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" t="s">
         <v>92</v>
       </c>
-      <c r="H31" t="s">
-        <v>93</v>
-      </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <v>1059</v>
+      </c>
+      <c r="D32" t="s">
         <v>94</v>
       </c>
-      <c r="B32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32">
-        <v>2754</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>95</v>
       </c>
-      <c r="E32" t="s">
-        <v>36</v>
-      </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" t="s">
         <v>96</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>97</v>
-      </c>
-      <c r="I32" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33">
+        <v>1058</v>
+      </c>
+      <c r="D33" t="s">
         <v>99</v>
       </c>
-      <c r="B33" t="s">
+      <c r="E33" t="s">
         <v>100</v>
       </c>
-      <c r="C33">
-        <v>2754</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>101</v>
-      </c>
-      <c r="E33" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
       </c>
       <c r="G33" t="s">
         <v>102</v>
@@ -1250,7 +1271,7 @@
         <v>103</v>
       </c>
       <c r="I33" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1258,28 +1279,28 @@
         <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C34">
-        <v>2754</v>
+        <v>1059</v>
       </c>
       <c r="D34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1287,231 +1308,231 @@
         <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C35">
-        <v>2756</v>
+        <v>1060</v>
       </c>
       <c r="D35" t="s">
         <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C36">
-        <v>2757</v>
+        <v>1059</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I36" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C37">
-        <v>2757</v>
+        <v>1058</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F37" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H37" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="C38">
-        <v>2756</v>
+        <v>1059</v>
       </c>
       <c r="D38" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="G38" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C39">
-        <v>2756</v>
+        <v>1059</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H39" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I39" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C40">
-        <v>2756</v>
+        <v>1058</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I40" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C41">
-        <v>2753</v>
+        <v>1056</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="E41" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I41" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C42">
-        <v>2755</v>
+        <v>1059</v>
       </c>
       <c r="D42" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H42" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
